--- a/Documentation/CoverModelEquations.xlsx
+++ b/Documentation/CoverModelEquations.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/astears/Documents/Dropbox_static/Work/NAU_USGS_postdoc/cleanPED/PED_vegClimModels/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CDBE62-CD7B-A742-A507-2BC19B2CADF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637A55A2-04F0-DE44-98B6-48D5AB403208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19780" xr2:uid="{11994C8F-3CB5-8346-9650-E956A8234D13}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="195">
   <si>
     <t>Response Variable</t>
   </si>
@@ -618,13 +618,19 @@
   </si>
   <si>
     <t>AWHC_scaled:clay_scaled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability of Treed (Continuous) </t>
+  </si>
+  <si>
+    <t>1/ (1 + exp(-(Intercept + Coefficient_1*Predictor_1 + … + Coefficient_n * Predictor_n)))/10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -640,23 +646,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="4">
@@ -706,18 +721,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1052,1915 +1070,2590 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19615024-B010-D046-8B02-06BF2AB91B4B}">
-  <dimension ref="A1:CP12"/>
+  <dimension ref="A1:CP13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="5"/>
-    <col min="2" max="2" width="47.6640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" style="5" customWidth="1"/>
-    <col min="4" max="5" width="10.83203125" style="6"/>
-    <col min="6" max="7" width="10.83203125" style="5"/>
-    <col min="8" max="9" width="10.83203125" style="6"/>
-    <col min="10" max="11" width="10.83203125" style="5"/>
-    <col min="12" max="13" width="10.83203125" style="6"/>
-    <col min="14" max="15" width="10.83203125" style="5"/>
-    <col min="16" max="17" width="10.83203125" style="6"/>
-    <col min="18" max="19" width="10.83203125" style="5"/>
-    <col min="20" max="21" width="10.83203125" style="6"/>
-    <col min="22" max="23" width="10.83203125" style="5"/>
-    <col min="24" max="25" width="10.83203125" style="6"/>
-    <col min="26" max="27" width="10.83203125" style="5"/>
-    <col min="28" max="29" width="10.83203125" style="6"/>
-    <col min="30" max="31" width="10.83203125" style="5"/>
-    <col min="32" max="33" width="10.83203125" style="6"/>
-    <col min="34" max="35" width="10.83203125" style="5"/>
-    <col min="36" max="37" width="10.83203125" style="6"/>
-    <col min="38" max="39" width="10.83203125" style="5"/>
-    <col min="40" max="41" width="10.83203125" style="6"/>
-    <col min="42" max="43" width="10.83203125" style="5"/>
-    <col min="44" max="45" width="10.83203125" style="6"/>
-    <col min="46" max="47" width="10.83203125" style="5"/>
-    <col min="48" max="49" width="10.83203125" style="6"/>
-    <col min="50" max="51" width="10.83203125" style="5"/>
-    <col min="52" max="53" width="10.83203125" style="6"/>
-    <col min="54" max="55" width="10.83203125" style="5"/>
-    <col min="56" max="57" width="10.83203125" style="6"/>
-    <col min="58" max="59" width="10.83203125" style="5"/>
-    <col min="60" max="61" width="10.83203125" style="6"/>
-    <col min="62" max="63" width="10.83203125" style="5"/>
-    <col min="64" max="65" width="10.83203125" style="6"/>
-    <col min="66" max="67" width="10.83203125" style="5"/>
-    <col min="68" max="69" width="10.83203125" style="6"/>
-    <col min="70" max="71" width="10.83203125" style="5"/>
-    <col min="72" max="73" width="10.83203125" style="6"/>
-    <col min="74" max="75" width="10.83203125" style="5"/>
-    <col min="76" max="77" width="10.83203125" style="6"/>
-    <col min="78" max="79" width="10.83203125" style="5"/>
-    <col min="80" max="81" width="10.83203125" style="6"/>
-    <col min="82" max="83" width="10.83203125" style="5"/>
-    <col min="84" max="85" width="10.83203125" style="6"/>
-    <col min="86" max="87" width="10.83203125" style="7"/>
-    <col min="88" max="89" width="10.83203125" style="6"/>
-    <col min="90" max="91" width="10.83203125" style="7"/>
-    <col min="92" max="93" width="10.83203125" style="6"/>
-    <col min="94" max="94" width="10.83203125" style="7"/>
-    <col min="95" max="16384" width="10.83203125" style="5"/>
+    <col min="1" max="1" width="10.83203125" style="2"/>
+    <col min="2" max="2" width="47.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="10.83203125" style="3"/>
+    <col min="6" max="7" width="10.83203125" style="2"/>
+    <col min="8" max="9" width="10.83203125" style="3"/>
+    <col min="10" max="11" width="10.83203125" style="2"/>
+    <col min="12" max="13" width="10.83203125" style="3"/>
+    <col min="14" max="15" width="10.83203125" style="2"/>
+    <col min="16" max="17" width="10.83203125" style="3"/>
+    <col min="18" max="19" width="10.83203125" style="2"/>
+    <col min="20" max="21" width="10.83203125" style="3"/>
+    <col min="22" max="23" width="10.83203125" style="2"/>
+    <col min="24" max="25" width="10.83203125" style="3"/>
+    <col min="26" max="27" width="10.83203125" style="2"/>
+    <col min="28" max="29" width="10.83203125" style="3"/>
+    <col min="30" max="31" width="10.83203125" style="2"/>
+    <col min="32" max="33" width="10.83203125" style="3"/>
+    <col min="34" max="35" width="10.83203125" style="2"/>
+    <col min="36" max="37" width="10.83203125" style="3"/>
+    <col min="38" max="39" width="10.83203125" style="2"/>
+    <col min="40" max="41" width="10.83203125" style="3"/>
+    <col min="42" max="43" width="10.83203125" style="2"/>
+    <col min="44" max="45" width="10.83203125" style="3"/>
+    <col min="46" max="47" width="10.83203125" style="2"/>
+    <col min="48" max="49" width="10.83203125" style="3"/>
+    <col min="50" max="51" width="10.83203125" style="2"/>
+    <col min="52" max="53" width="10.83203125" style="3"/>
+    <col min="54" max="55" width="10.83203125" style="2"/>
+    <col min="56" max="57" width="10.83203125" style="3"/>
+    <col min="58" max="59" width="10.83203125" style="2"/>
+    <col min="60" max="61" width="10.83203125" style="3"/>
+    <col min="62" max="63" width="10.83203125" style="2"/>
+    <col min="64" max="65" width="10.83203125" style="3"/>
+    <col min="66" max="67" width="10.83203125" style="2"/>
+    <col min="68" max="69" width="10.83203125" style="3"/>
+    <col min="70" max="71" width="10.83203125" style="2"/>
+    <col min="72" max="73" width="10.83203125" style="3"/>
+    <col min="74" max="75" width="10.83203125" style="2"/>
+    <col min="76" max="77" width="10.83203125" style="3"/>
+    <col min="78" max="79" width="10.83203125" style="2"/>
+    <col min="80" max="81" width="10.83203125" style="3"/>
+    <col min="82" max="83" width="10.83203125" style="2"/>
+    <col min="84" max="85" width="10.83203125" style="3"/>
+    <col min="86" max="87" width="10.83203125" style="4"/>
+    <col min="88" max="89" width="10.83203125" style="3"/>
+    <col min="90" max="91" width="10.83203125" style="4"/>
+    <col min="92" max="93" width="10.83203125" style="3"/>
+    <col min="94" max="94" width="10.83203125" style="4"/>
+    <col min="95" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:94" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AH1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AI1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="AL1" s="4" t="s">
+      <c r="AL1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="AM1" s="4" t="s">
+      <c r="AM1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AN1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="AP1" s="4" t="s">
+      <c r="AP1" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="AQ1" s="4" t="s">
+      <c r="AQ1" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AR1" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AS1" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="AT1" s="4" t="s">
+      <c r="AT1" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="AU1" s="4" t="s">
+      <c r="AU1" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AV1" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AW1" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="AX1" s="4" t="s">
+      <c r="AX1" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="AY1" s="4" t="s">
+      <c r="AY1" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="AZ1" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BA1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="BB1" s="4" t="s">
+      <c r="BB1" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="BC1" s="4" t="s">
+      <c r="BC1" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BD1" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BE1" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="BF1" s="4" t="s">
+      <c r="BF1" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="BG1" s="4" t="s">
+      <c r="BG1" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BH1" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="BI1" s="3" t="s">
+      <c r="BI1" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="BJ1" s="4" t="s">
+      <c r="BJ1" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="BK1" s="4" t="s">
+      <c r="BK1" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="BL1" s="3" t="s">
+      <c r="BL1" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="BM1" s="3" t="s">
+      <c r="BM1" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="BN1" s="4" t="s">
+      <c r="BN1" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="BO1" s="4" t="s">
+      <c r="BO1" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="BP1" s="3" t="s">
+      <c r="BP1" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="BQ1" s="3" t="s">
+      <c r="BQ1" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="BR1" s="4" t="s">
+      <c r="BR1" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="BS1" s="4" t="s">
+      <c r="BS1" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="BT1" s="3" t="s">
+      <c r="BT1" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="BU1" s="3" t="s">
+      <c r="BU1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="BV1" s="4" t="s">
+      <c r="BV1" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BW1" s="4" t="s">
+      <c r="BW1" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="BX1" s="3" t="s">
+      <c r="BX1" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="BY1" s="3" t="s">
+      <c r="BY1" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="BZ1" s="4" t="s">
+      <c r="BZ1" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="CA1" s="4" t="s">
+      <c r="CA1" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="CB1" s="3" t="s">
+      <c r="CB1" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="CC1" s="3" t="s">
+      <c r="CC1" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="CD1" s="4" t="s">
+      <c r="CD1" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="CE1" s="4" t="s">
+      <c r="CE1" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="CF1" s="3" t="s">
+      <c r="CF1" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="CG1" s="3" t="s">
+      <c r="CG1" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="CH1" s="4" t="s">
+      <c r="CH1" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="CI1" s="4" t="s">
+      <c r="CI1" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="CJ1" s="3" t="s">
+      <c r="CJ1" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="CK1" s="3" t="s">
+      <c r="CK1" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="CL1" s="4" t="s">
+      <c r="CL1" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="CM1" s="4" t="s">
+      <c r="CM1" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="CN1" s="3" t="s">
+      <c r="CN1" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="CO1" s="3" t="s">
+      <c r="CO1" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="CP1" s="8" t="s">
+      <c r="CP1" s="9" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:94" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="10">
         <v>3.3856549999999999</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="11">
         <f>-0.798222</f>
         <v>-0.79822199999999999</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="10">
         <v>4.7453609999999999</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="11">
         <v>-0.49798700000000001</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="10">
         <v>0.22745499999999999</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="11">
         <v>-0.390513</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="10">
         <v>0.53857100000000002</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="11">
         <v>-0.40059800000000001</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="10">
         <v>-0.83406999999999998</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="S2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="T2" s="6">
+      <c r="T2" s="11">
         <v>-0.94850299999999999</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="V2" s="5">
+      <c r="V2" s="10">
         <v>0.19450600000000001</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="W2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="X2" s="6">
+      <c r="X2" s="11">
         <v>-4.7726999999999999E-2</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Y2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="Z2" s="5">
+      <c r="Z2" s="10">
         <v>-0.26519999999999999</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AA2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AB2" s="6">
+      <c r="AB2" s="11">
         <v>7.4388999999999997E-2</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="AC2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="AD2" s="5">
+      <c r="AD2" s="10">
         <v>-0.29049799999999998</v>
       </c>
-      <c r="AE2" s="5" t="s">
+      <c r="AE2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="AF2" s="6">
+      <c r="AF2" s="11">
         <v>-0.16800599999999999</v>
       </c>
-      <c r="AG2" s="6" t="s">
+      <c r="AG2" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="AH2" s="5">
+      <c r="AH2" s="10">
         <v>7.6255000000000003E-2</v>
       </c>
-      <c r="AI2" s="5" t="s">
+      <c r="AI2" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AJ2" s="6">
+      <c r="AJ2" s="11">
         <v>-0.55536200000000002</v>
       </c>
-      <c r="AK2" s="6" t="s">
+      <c r="AK2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="AL2" s="5">
+      <c r="AL2" s="10">
         <v>-0.37720999999999999</v>
       </c>
-      <c r="AM2" s="5" t="s">
+      <c r="AM2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="CP2" s="7" t="s">
+      <c r="AN2" s="11"/>
+      <c r="AO2" s="11"/>
+      <c r="AP2" s="10"/>
+      <c r="AQ2" s="10"/>
+      <c r="AR2" s="11"/>
+      <c r="AS2" s="11"/>
+      <c r="AT2" s="10"/>
+      <c r="AU2" s="10"/>
+      <c r="AV2" s="11"/>
+      <c r="AW2" s="11"/>
+      <c r="AX2" s="10"/>
+      <c r="AY2" s="10"/>
+      <c r="AZ2" s="11"/>
+      <c r="BA2" s="11"/>
+      <c r="BB2" s="10"/>
+      <c r="BC2" s="10"/>
+      <c r="BD2" s="11"/>
+      <c r="BE2" s="11"/>
+      <c r="BF2" s="10"/>
+      <c r="BG2" s="10"/>
+      <c r="BH2" s="11"/>
+      <c r="BI2" s="11"/>
+      <c r="BJ2" s="10"/>
+      <c r="BK2" s="10"/>
+      <c r="BL2" s="11"/>
+      <c r="BM2" s="11"/>
+      <c r="BN2" s="10"/>
+      <c r="BO2" s="10"/>
+      <c r="BP2" s="11"/>
+      <c r="BQ2" s="11"/>
+      <c r="BR2" s="10"/>
+      <c r="BS2" s="10"/>
+      <c r="BT2" s="11"/>
+      <c r="BU2" s="11"/>
+      <c r="BV2" s="10"/>
+      <c r="BW2" s="10"/>
+      <c r="BX2" s="11"/>
+      <c r="BY2" s="11"/>
+      <c r="BZ2" s="10"/>
+      <c r="CA2" s="10"/>
+      <c r="CB2" s="11"/>
+      <c r="CC2" s="11"/>
+      <c r="CD2" s="10"/>
+      <c r="CE2" s="10"/>
+      <c r="CF2" s="11"/>
+      <c r="CG2" s="11"/>
+      <c r="CH2" s="12"/>
+      <c r="CI2" s="12"/>
+      <c r="CJ2" s="11"/>
+      <c r="CK2" s="11"/>
+      <c r="CL2" s="12"/>
+      <c r="CM2" s="12"/>
+      <c r="CN2" s="11"/>
+      <c r="CO2" s="11"/>
+      <c r="CP2" s="12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:94" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5">
-        <v>-0.14550162</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0.39496901000000001</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0.45402154</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H3" s="6">
-        <v>-3.774131E-2</v>
-      </c>
-      <c r="I3" s="6" t="s">
+      <c r="B3" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="13">
+        <v>2.9585593800000001</v>
+      </c>
+      <c r="D3" s="11">
+        <v>4.0782501399999997</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="10">
+        <v>-0.52045534999999998</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0.23144659000000001</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="5">
-        <v>-0.19073238000000001</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="L3" s="6">
-        <v>-3.9033449999999997E-2</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="N3" s="5">
-        <v>4.925156E-2</v>
-      </c>
-      <c r="O3" s="5" t="s">
+      <c r="J3" s="10">
+        <v>-0.24275564999999999</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="11">
+        <v>0.21184654</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="10">
+        <v>-0.53480691000000002</v>
+      </c>
+      <c r="O3" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="P3" s="6">
-        <v>-8.0673439999999999E-2</v>
-      </c>
-      <c r="Q3" s="6" t="s">
+      <c r="P3" s="11">
+        <v>-7.5538100000000002E-3</v>
+      </c>
+      <c r="Q3" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="R3" s="5">
-        <v>-4.8379980000000003E-2</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="T3" s="6">
-        <v>-0.17399395000000001</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="V3" s="5">
-        <v>0.15772348999999999</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="X3" s="6">
-        <v>-0.14900854999999999</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="CP3" s="7" t="s">
+      <c r="R3" s="10">
+        <v>-0.79109390999999996</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="11">
+        <v>-0.94834744000000004</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="V3" s="10">
+        <v>0.51546188999999998</v>
+      </c>
+      <c r="W3" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="X3" s="11">
+        <v>-2.6416329999999998E-2</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z3" s="10">
+        <v>-0.29985365000000003</v>
+      </c>
+      <c r="AA3" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB3" s="11">
+        <v>6.3699930000000002E-2</v>
+      </c>
+      <c r="AC3" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="11"/>
+      <c r="AG3" s="11"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="11"/>
+      <c r="AK3" s="11"/>
+      <c r="AL3" s="10"/>
+      <c r="AM3" s="10"/>
+      <c r="AN3" s="11"/>
+      <c r="AO3" s="11"/>
+      <c r="AP3" s="10"/>
+      <c r="AQ3" s="10"/>
+      <c r="AR3" s="11"/>
+      <c r="AS3" s="11"/>
+      <c r="AT3" s="10"/>
+      <c r="AU3" s="10"/>
+      <c r="AV3" s="11"/>
+      <c r="AW3" s="11"/>
+      <c r="AX3" s="10"/>
+      <c r="AY3" s="10"/>
+      <c r="AZ3" s="11"/>
+      <c r="BA3" s="11"/>
+      <c r="BB3" s="10"/>
+      <c r="BC3" s="10"/>
+      <c r="BD3" s="11"/>
+      <c r="BE3" s="11"/>
+      <c r="BF3" s="10"/>
+      <c r="BG3" s="10"/>
+      <c r="BH3" s="11"/>
+      <c r="BI3" s="11"/>
+      <c r="BJ3" s="10"/>
+      <c r="BK3" s="10"/>
+      <c r="BL3" s="11"/>
+      <c r="BM3" s="11"/>
+      <c r="BN3" s="10"/>
+      <c r="BO3" s="10"/>
+      <c r="BP3" s="11"/>
+      <c r="BQ3" s="11"/>
+      <c r="BR3" s="10"/>
+      <c r="BS3" s="10"/>
+      <c r="BT3" s="11"/>
+      <c r="BU3" s="11"/>
+      <c r="BV3" s="10"/>
+      <c r="BW3" s="10"/>
+      <c r="BX3" s="11"/>
+      <c r="BY3" s="11"/>
+      <c r="BZ3" s="10"/>
+      <c r="CA3" s="10"/>
+      <c r="CB3" s="11"/>
+      <c r="CC3" s="11"/>
+      <c r="CD3" s="10"/>
+      <c r="CE3" s="10"/>
+      <c r="CF3" s="11"/>
+      <c r="CG3" s="11"/>
+      <c r="CH3" s="12"/>
+      <c r="CI3" s="12"/>
+      <c r="CJ3" s="11"/>
+      <c r="CK3" s="11"/>
+      <c r="CL3" s="12"/>
+      <c r="CM3" s="12"/>
+      <c r="CN3" s="11"/>
+      <c r="CO3" s="11"/>
+      <c r="CP3" s="12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:94" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0.56998409900000002</v>
-      </c>
-      <c r="D4" s="6">
-        <v>0.51250426699999996</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="5">
-        <v>1.431187175</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="B4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10">
+        <v>-0.14550162</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0.39496901000000001</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0.45402154</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="H4" s="6">
-        <v>-1.5606823000000001E-2</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="5">
-        <v>8.5489657999999996E-2</v>
-      </c>
-      <c r="K4" s="5" t="s">
+      <c r="H4" s="11">
+        <v>-3.774131E-2</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="6">
-        <v>0.42561744600000001</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" s="5">
-        <v>0.193781017</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="6">
-        <v>-0.29890401300000002</v>
-      </c>
-      <c r="Q4" s="6" t="s">
+      <c r="J4" s="10">
+        <v>-0.19073238000000001</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="L4" s="11">
+        <v>-3.9033449999999997E-2</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="N4" s="10">
+        <v>4.925156E-2</v>
+      </c>
+      <c r="O4" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="R4" s="5">
-        <v>0.102872246</v>
-      </c>
-      <c r="S4" s="5" t="s">
+      <c r="P4" s="11">
+        <v>-8.0673439999999999E-2</v>
+      </c>
+      <c r="Q4" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="T4" s="6">
-        <v>-1.680676155</v>
-      </c>
-      <c r="U4" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="V4" s="5">
-        <v>-0.115506761</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="X4" s="6">
-        <v>0.213916301</v>
-      </c>
-      <c r="Y4" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z4" s="5">
-        <v>-0.10504277099999999</v>
-      </c>
-      <c r="AA4" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB4" s="6">
-        <v>-6.4530063999999998E-2</v>
-      </c>
-      <c r="AC4" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD4" s="5">
-        <v>4.6608029999999998E-3</v>
-      </c>
-      <c r="AE4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF4" s="6">
-        <v>-0.31603266800000002</v>
-      </c>
-      <c r="AG4" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="AH4" s="5">
-        <v>-0.47956990700000002</v>
-      </c>
-      <c r="AI4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="AJ4" s="6">
-        <v>0.42334626400000003</v>
-      </c>
-      <c r="AK4" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="AL4" s="5">
-        <v>1.4904278999999999E-2</v>
-      </c>
-      <c r="AM4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN4" s="6">
-        <v>0.25526795099999999</v>
-      </c>
-      <c r="AO4" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="CP4" s="7" t="s">
+      <c r="R4" s="10">
+        <v>-4.8379980000000003E-2</v>
+      </c>
+      <c r="S4" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="T4" s="11">
+        <v>-0.17399395000000001</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="V4" s="10">
+        <v>0.15772348999999999</v>
+      </c>
+      <c r="W4" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="X4" s="11">
+        <v>-0.14900854999999999</v>
+      </c>
+      <c r="Y4" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="11"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="10"/>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="10"/>
+      <c r="AI4" s="10"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="10"/>
+      <c r="AM4" s="10"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="10"/>
+      <c r="AQ4" s="10"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="10"/>
+      <c r="AU4" s="10"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="10"/>
+      <c r="AY4" s="10"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="10"/>
+      <c r="BC4" s="10"/>
+      <c r="BD4" s="11"/>
+      <c r="BE4" s="11"/>
+      <c r="BF4" s="10"/>
+      <c r="BG4" s="10"/>
+      <c r="BH4" s="11"/>
+      <c r="BI4" s="11"/>
+      <c r="BJ4" s="10"/>
+      <c r="BK4" s="10"/>
+      <c r="BL4" s="11"/>
+      <c r="BM4" s="11"/>
+      <c r="BN4" s="10"/>
+      <c r="BO4" s="10"/>
+      <c r="BP4" s="11"/>
+      <c r="BQ4" s="11"/>
+      <c r="BR4" s="10"/>
+      <c r="BS4" s="10"/>
+      <c r="BT4" s="11"/>
+      <c r="BU4" s="11"/>
+      <c r="BV4" s="10"/>
+      <c r="BW4" s="10"/>
+      <c r="BX4" s="11"/>
+      <c r="BY4" s="11"/>
+      <c r="BZ4" s="10"/>
+      <c r="CA4" s="10"/>
+      <c r="CB4" s="11"/>
+      <c r="CC4" s="11"/>
+      <c r="CD4" s="10"/>
+      <c r="CE4" s="10"/>
+      <c r="CF4" s="11"/>
+      <c r="CG4" s="11"/>
+      <c r="CH4" s="12"/>
+      <c r="CI4" s="12"/>
+      <c r="CJ4" s="11"/>
+      <c r="CK4" s="11"/>
+      <c r="CL4" s="12"/>
+      <c r="CM4" s="12"/>
+      <c r="CN4" s="11"/>
+      <c r="CO4" s="11"/>
+      <c r="CP4" s="12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:94" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5">
-        <v>-0.71945199999999998</v>
-      </c>
-      <c r="D5" s="6">
-        <v>-0.31914999999999999</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="B5" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="10">
+        <v>0.56998409900000002</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0.51250426699999996</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="5">
-        <v>-0.70535599999999998</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="6">
-        <v>2.2533000000000001E-2</v>
-      </c>
-      <c r="I5" s="6" t="s">
+      <c r="F5" s="10">
+        <v>1.431187175</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H5" s="11">
+        <v>-1.5606823000000001E-2</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="5">
-        <v>-0.130411</v>
-      </c>
-      <c r="K5" s="5" t="s">
+      <c r="J5" s="10">
+        <v>8.5489657999999996E-2</v>
+      </c>
+      <c r="K5" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="L5" s="6">
-        <v>1.0504119999999999</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="N5" s="5">
-        <v>0.14322799999999999</v>
-      </c>
-      <c r="O5" s="5" t="s">
+      <c r="L5" s="11">
+        <v>0.42561744600000001</v>
+      </c>
+      <c r="M5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="P5" s="6">
-        <v>-0.18015300000000001</v>
-      </c>
-      <c r="Q5" s="6" t="s">
+      <c r="N5" s="10">
+        <v>0.193781017</v>
+      </c>
+      <c r="O5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R5" s="5">
-        <v>3.5943999999999997E-2</v>
-      </c>
-      <c r="S5" s="5" t="s">
+      <c r="P5" s="11">
+        <v>-0.29890401300000002</v>
+      </c>
+      <c r="Q5" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="T5" s="6">
-        <v>1.0501999999999999E-2</v>
-      </c>
-      <c r="U5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="V5" s="5">
-        <v>-1.9455E-2</v>
-      </c>
-      <c r="W5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="X5" s="6">
-        <v>-5.4052000000000003E-2</v>
-      </c>
-      <c r="Y5" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z5" s="5">
-        <v>-9.0100000000000006E-3</v>
-      </c>
-      <c r="AA5" s="5" t="s">
+      <c r="R5" s="10">
+        <v>0.102872246</v>
+      </c>
+      <c r="S5" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AB5" s="6">
-        <v>0.16358700000000001</v>
-      </c>
-      <c r="AC5" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD5" s="5">
-        <v>0.48485899999999998</v>
-      </c>
-      <c r="AE5" s="5" t="s">
+      <c r="T5" s="11">
+        <v>-1.680676155</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="V5" s="10">
+        <v>-0.115506761</v>
+      </c>
+      <c r="W5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF5" s="6">
-        <v>-0.12725400000000001</v>
-      </c>
-      <c r="AG5" s="6" t="s">
+      <c r="X5" s="11">
+        <v>0.213916301</v>
+      </c>
+      <c r="Y5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="AH5" s="5">
-        <v>-0.458708</v>
-      </c>
-      <c r="AI5" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ5" s="6">
-        <v>-3.3515000000000003E-2</v>
-      </c>
-      <c r="AK5" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL5" s="5">
-        <v>-2.4780000000000002E-3</v>
-      </c>
-      <c r="AM5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AN5" s="6">
-        <v>-4.2849999999999997E-3</v>
-      </c>
-      <c r="AO5" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="AP5" s="5">
-        <v>3.5408000000000002E-2</v>
-      </c>
-      <c r="AQ5" s="5" t="s">
+      <c r="Z5" s="10">
+        <v>-0.10504277099999999</v>
+      </c>
+      <c r="AA5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="AR5" s="6">
-        <v>7.7843999999999997E-2</v>
-      </c>
-      <c r="AS5" s="6" t="s">
+      <c r="AB5" s="11">
+        <v>-6.4530063999999998E-2</v>
+      </c>
+      <c r="AC5" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="AT5" s="5">
-        <v>-9.7524E-2</v>
-      </c>
-      <c r="AU5" s="5" t="s">
+      <c r="AD5" s="10">
+        <v>4.6608029999999998E-3</v>
+      </c>
+      <c r="AE5" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AV5" s="6">
-        <v>0.16988900000000001</v>
-      </c>
-      <c r="AW5" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX5" s="5">
-        <v>-0.11025</v>
-      </c>
-      <c r="AY5" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AZ5" s="6">
-        <v>-5.3682000000000001E-2</v>
-      </c>
-      <c r="BA5" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BB5" s="5">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="BC5" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="BD5" s="6">
-        <v>5.4327E-2</v>
-      </c>
-      <c r="BE5" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="BF5" s="5">
-        <v>5.6779999999999999E-3</v>
-      </c>
-      <c r="BG5" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="BH5" s="6">
-        <v>-7.3850000000000001E-3</v>
-      </c>
-      <c r="BI5" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="BJ5" s="5">
-        <v>-1.3277000000000001E-2</v>
-      </c>
-      <c r="BK5" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="BL5" s="6">
-        <v>-1.1660999999999999E-2</v>
-      </c>
-      <c r="BM5" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="BN5" s="5">
-        <v>-4.4780000000000002E-3</v>
-      </c>
-      <c r="BO5" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP5" s="6">
-        <v>6.8477999999999997E-2</v>
-      </c>
-      <c r="BQ5" s="6" t="s">
+      <c r="AF5" s="11">
+        <v>-0.31603266800000002</v>
+      </c>
+      <c r="AG5" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="BR5" s="5">
-        <v>-2.3970000000000002E-2</v>
-      </c>
-      <c r="BS5" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="BT5" s="6">
-        <v>9.2974000000000001E-2</v>
-      </c>
-      <c r="BU5" s="6" t="s">
+      <c r="AH5" s="10">
+        <v>-0.47956990700000002</v>
+      </c>
+      <c r="AI5" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="BV5" s="5">
-        <v>2.8679999999999999E-3</v>
-      </c>
-      <c r="BW5" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="BX5" s="6">
-        <v>3.5399999999999999E-4</v>
-      </c>
-      <c r="BY5" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="BZ5" s="5">
-        <v>4.4149999999999997E-3</v>
-      </c>
-      <c r="CA5" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="CB5" s="6">
-        <v>-5.9589999999999999E-3</v>
-      </c>
-      <c r="CC5" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="CD5" s="5">
-        <v>0.245366</v>
-      </c>
-      <c r="CE5" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="CF5" s="6">
-        <v>-1.3035E-2</v>
-      </c>
-      <c r="CG5" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="CH5" s="7">
-        <v>-0.12500600000000001</v>
-      </c>
-      <c r="CI5" s="7" t="s">
+      <c r="AJ5" s="11">
+        <v>0.42334626400000003</v>
+      </c>
+      <c r="AK5" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="CJ5" s="6">
-        <v>-5.5662000000000003E-2</v>
-      </c>
-      <c r="CK5" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="CL5" s="7">
-        <v>-5.0639999999999998E-2</v>
-      </c>
-      <c r="CM5" s="7" t="s">
+      <c r="AL5" s="10">
+        <v>1.4904278999999999E-2</v>
+      </c>
+      <c r="AM5" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="CN5" s="6">
-        <v>0.112549</v>
-      </c>
-      <c r="CO5" s="6" t="s">
+      <c r="AN5" s="11">
+        <v>0.25526795099999999</v>
+      </c>
+      <c r="AO5" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="CP5" s="7" t="s">
-        <v>67</v>
+      <c r="AP5" s="10"/>
+      <c r="AQ5" s="10"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="10"/>
+      <c r="AU5" s="10"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="10"/>
+      <c r="AY5" s="10"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="10"/>
+      <c r="BC5" s="10"/>
+      <c r="BD5" s="11"/>
+      <c r="BE5" s="11"/>
+      <c r="BF5" s="10"/>
+      <c r="BG5" s="10"/>
+      <c r="BH5" s="11"/>
+      <c r="BI5" s="11"/>
+      <c r="BJ5" s="10"/>
+      <c r="BK5" s="10"/>
+      <c r="BL5" s="11"/>
+      <c r="BM5" s="11"/>
+      <c r="BN5" s="10"/>
+      <c r="BO5" s="10"/>
+      <c r="BP5" s="11"/>
+      <c r="BQ5" s="11"/>
+      <c r="BR5" s="10"/>
+      <c r="BS5" s="10"/>
+      <c r="BT5" s="11"/>
+      <c r="BU5" s="11"/>
+      <c r="BV5" s="10"/>
+      <c r="BW5" s="10"/>
+      <c r="BX5" s="11"/>
+      <c r="BY5" s="11"/>
+      <c r="BZ5" s="10"/>
+      <c r="CA5" s="10"/>
+      <c r="CB5" s="11"/>
+      <c r="CC5" s="11"/>
+      <c r="CD5" s="10"/>
+      <c r="CE5" s="10"/>
+      <c r="CF5" s="11"/>
+      <c r="CG5" s="11"/>
+      <c r="CH5" s="12"/>
+      <c r="CI5" s="12"/>
+      <c r="CJ5" s="11"/>
+      <c r="CK5" s="11"/>
+      <c r="CL5" s="12"/>
+      <c r="CM5" s="12"/>
+      <c r="CN5" s="11"/>
+      <c r="CO5" s="11"/>
+      <c r="CP5" s="12" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:94" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="5">
-        <v>-2.8047295600000002</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0.13655018999999999</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="B6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="10">
+        <v>-0.71945199999999998</v>
+      </c>
+      <c r="D6" s="11">
+        <v>-0.31914999999999999</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="5">
-        <v>-0.60869165999999997</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="F6" s="10">
+        <v>-0.70535599999999998</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="6">
-        <v>0.38908060999999999</v>
-      </c>
-      <c r="I6" s="6" t="s">
+      <c r="H6" s="11">
+        <v>2.2533000000000001E-2</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="10">
+        <v>-0.130411</v>
+      </c>
+      <c r="K6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="5">
-        <v>-1.0734355099999999</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="L6" s="6">
-        <v>-0.31898110000000002</v>
-      </c>
-      <c r="M6" s="6" t="s">
+      <c r="L6" s="11">
+        <v>1.0504119999999999</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="10">
+        <v>0.14322799999999999</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" s="11">
+        <v>-0.18015300000000001</v>
+      </c>
+      <c r="Q6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="5">
-        <v>5.583258E-2</v>
-      </c>
-      <c r="O6" s="5" t="s">
+      <c r="R6" s="10">
+        <v>3.5943999999999997E-2</v>
+      </c>
+      <c r="S6" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="P6" s="6">
-        <v>-0.11323576</v>
-      </c>
-      <c r="Q6" s="6" t="s">
+      <c r="T6" s="11">
+        <v>1.0501999999999999E-2</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="V6" s="10">
+        <v>-1.9455E-2</v>
+      </c>
+      <c r="W6" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="X6" s="11">
+        <v>-5.4052000000000003E-2</v>
+      </c>
+      <c r="Y6" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z6" s="10">
+        <v>-9.0100000000000006E-3</v>
+      </c>
+      <c r="AA6" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="R6" s="5">
-        <v>0.10614274</v>
-      </c>
-      <c r="S6" s="5" t="s">
+      <c r="AB6" s="11">
+        <v>0.16358700000000001</v>
+      </c>
+      <c r="AC6" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="T6" s="6">
-        <v>-0.20983375000000001</v>
-      </c>
-      <c r="U6" s="6" t="s">
+      <c r="AD6" s="10">
+        <v>0.48485899999999998</v>
+      </c>
+      <c r="AE6" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V6" s="5">
-        <v>-0.10582749</v>
-      </c>
-      <c r="W6" s="5" t="s">
+      <c r="AF6" s="11">
+        <v>-0.12725400000000001</v>
+      </c>
+      <c r="AG6" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="X6" s="6">
-        <v>0.33306324999999998</v>
-      </c>
-      <c r="Y6" s="6" t="s">
+      <c r="AH6" s="10">
+        <v>-0.458708</v>
+      </c>
+      <c r="AI6" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="Z6" s="5">
-        <v>1.6354879999999999E-2</v>
-      </c>
-      <c r="AA6" s="5" t="s">
+      <c r="AJ6" s="11">
+        <v>-3.3515000000000003E-2</v>
+      </c>
+      <c r="AK6" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL6" s="10">
+        <v>-2.4780000000000002E-3</v>
+      </c>
+      <c r="AM6" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN6" s="11">
+        <v>-4.2849999999999997E-3</v>
+      </c>
+      <c r="AO6" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP6" s="10">
+        <v>3.5408000000000002E-2</v>
+      </c>
+      <c r="AQ6" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="AB6" s="6">
-        <v>3.7831400000000001E-2</v>
-      </c>
-      <c r="AC6" s="6" t="s">
+      <c r="AR6" s="11">
+        <v>7.7843999999999997E-2</v>
+      </c>
+      <c r="AS6" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="AD6" s="5">
-        <v>6.1580490000000002E-2</v>
-      </c>
-      <c r="AE6" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="AF6" s="6">
-        <v>-0.23786667</v>
-      </c>
-      <c r="AG6" s="6" t="s">
+      <c r="AT6" s="10">
+        <v>-9.7524E-2</v>
+      </c>
+      <c r="AU6" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="AV6" s="11">
+        <v>0.16988900000000001</v>
+      </c>
+      <c r="AW6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX6" s="10">
+        <v>-0.11025</v>
+      </c>
+      <c r="AY6" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AZ6" s="11">
+        <v>-5.3682000000000001E-2</v>
+      </c>
+      <c r="BA6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="BB6" s="10">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="BC6" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="BD6" s="11">
+        <v>5.4327E-2</v>
+      </c>
+      <c r="BE6" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="BF6" s="10">
+        <v>5.6779999999999999E-3</v>
+      </c>
+      <c r="BG6" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="BH6" s="11">
+        <v>-7.3850000000000001E-3</v>
+      </c>
+      <c r="BI6" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="BJ6" s="10">
+        <v>-1.3277000000000001E-2</v>
+      </c>
+      <c r="BK6" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL6" s="11">
+        <v>-1.1660999999999999E-2</v>
+      </c>
+      <c r="BM6" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="BN6" s="10">
+        <v>-4.4780000000000002E-3</v>
+      </c>
+      <c r="BO6" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="BP6" s="11">
+        <v>6.8477999999999997E-2</v>
+      </c>
+      <c r="BQ6" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="BR6" s="10">
+        <v>-2.3970000000000002E-2</v>
+      </c>
+      <c r="BS6" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="BT6" s="11">
+        <v>9.2974000000000001E-2</v>
+      </c>
+      <c r="BU6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="BV6" s="10">
+        <v>2.8679999999999999E-3</v>
+      </c>
+      <c r="BW6" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="BX6" s="11">
+        <v>3.5399999999999999E-4</v>
+      </c>
+      <c r="BY6" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="BZ6" s="10">
+        <v>4.4149999999999997E-3</v>
+      </c>
+      <c r="CA6" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="CB6" s="11">
+        <v>-5.9589999999999999E-3</v>
+      </c>
+      <c r="CC6" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="CD6" s="10">
+        <v>0.245366</v>
+      </c>
+      <c r="CE6" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="AH6" s="5">
-        <v>0.15430669</v>
-      </c>
-      <c r="AI6" s="5" t="s">
+      <c r="CF6" s="11">
+        <v>-1.3035E-2</v>
+      </c>
+      <c r="CG6" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="CH6" s="12">
+        <v>-0.12500600000000001</v>
+      </c>
+      <c r="CI6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="AJ6" s="6">
-        <v>1.8120939999999999E-2</v>
-      </c>
-      <c r="AK6" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="CP6" s="7" t="s">
+      <c r="CJ6" s="11">
+        <v>-5.5662000000000003E-2</v>
+      </c>
+      <c r="CK6" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="CL6" s="12">
+        <v>-5.0639999999999998E-2</v>
+      </c>
+      <c r="CM6" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="CN6" s="11">
+        <v>0.112549</v>
+      </c>
+      <c r="CO6" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="CP6" s="12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:94" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-1.279741325</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0.197935</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="B7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="10">
+        <v>-2.8047295600000002</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.13655018999999999</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="5">
-        <v>0.522922</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="F7" s="10">
+        <v>-0.60869165999999997</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="6">
-        <v>-0.31161100000000003</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0.102231</v>
-      </c>
-      <c r="K7" s="5" t="s">
+      <c r="H7" s="11">
+        <v>0.38908060999999999</v>
+      </c>
+      <c r="I7" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="6">
-        <v>-0.30405599999999999</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="N7" s="5">
-        <v>-0.135656</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="P7" s="6">
-        <v>0.15152099999999999</v>
-      </c>
-      <c r="Q7" s="6" t="s">
+      <c r="J7" s="10">
+        <v>-1.0734355099999999</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="L7" s="11">
+        <v>-0.31898110000000002</v>
+      </c>
+      <c r="M7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="R7" s="5">
-        <v>-1.0688E-2</v>
-      </c>
-      <c r="S7" s="5" t="s">
+      <c r="N7" s="10">
+        <v>5.583258E-2</v>
+      </c>
+      <c r="O7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="T7" s="6">
-        <v>1.5807999999999999E-2</v>
-      </c>
-      <c r="U7" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="V7" s="5">
-        <v>-2.9120000000000001E-3</v>
-      </c>
-      <c r="W7" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="X7" s="6">
-        <v>6.6180000000000003E-2</v>
-      </c>
-      <c r="Y7" s="6" t="s">
+      <c r="P7" s="11">
+        <v>-0.11323576</v>
+      </c>
+      <c r="Q7" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="Z7" s="5">
-        <v>2.1853000000000001E-2</v>
-      </c>
-      <c r="AA7" s="5" t="s">
+      <c r="R7" s="10">
+        <v>0.10614274</v>
+      </c>
+      <c r="S7" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="AB7" s="6">
-        <v>-0.16267000000000001</v>
-      </c>
-      <c r="AC7" s="6" t="s">
+      <c r="T7" s="11">
+        <v>-0.20983375000000001</v>
+      </c>
+      <c r="U7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="AD7" s="5">
-        <v>-3.2946000000000003E-2</v>
-      </c>
-      <c r="AE7" s="5" t="s">
+      <c r="V7" s="10">
+        <v>-0.10582749</v>
+      </c>
+      <c r="W7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="AF7" s="6">
-        <v>-0.22675500000000001</v>
-      </c>
-      <c r="AG7" s="6" t="s">
+      <c r="X7" s="11">
+        <v>0.33306324999999998</v>
+      </c>
+      <c r="Y7" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="AH7" s="5">
-        <v>2.3600000000000001E-3</v>
-      </c>
-      <c r="AI7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ7" s="6">
-        <v>8.8579999999999996E-3</v>
-      </c>
-      <c r="AK7" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AL7" s="5">
-        <v>-1.5839999999999999E-3</v>
-      </c>
-      <c r="AM7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="AN7" s="6">
-        <v>-2.8802999999999999E-2</v>
-      </c>
-      <c r="AO7" s="6" t="s">
+      <c r="Z7" s="10">
+        <v>1.6354879999999999E-2</v>
+      </c>
+      <c r="AA7" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="AP7" s="5">
-        <v>-0.10467</v>
-      </c>
-      <c r="AQ7" s="5" t="s">
+      <c r="AB7" s="11">
+        <v>3.7831400000000001E-2</v>
+      </c>
+      <c r="AC7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="AR7" s="6">
-        <v>-6.3159000000000007E-2</v>
-      </c>
-      <c r="AS7" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AT7" s="5">
-        <v>0.101286</v>
-      </c>
-      <c r="AU7" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="AV7" s="6">
-        <v>-0.48324499999999998</v>
-      </c>
-      <c r="AW7" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="AX7" s="5">
-        <v>0.25268099999999999</v>
-      </c>
-      <c r="AY7" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="AZ7" s="6">
-        <v>-2.043E-2</v>
-      </c>
-      <c r="BA7" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BB7" s="5">
-        <v>-7.6369999999999997E-3</v>
-      </c>
-      <c r="BC7" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="BD7" s="6">
-        <v>-5.1500000000000001E-3</v>
-      </c>
-      <c r="BE7" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="BF7" s="5">
-        <v>-1.7129999999999999E-3</v>
-      </c>
-      <c r="BG7" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="BH7" s="6">
-        <v>-5.9748999999999997E-2</v>
-      </c>
-      <c r="BI7" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="BJ7" s="5">
-        <v>-7.4051000000000006E-2</v>
-      </c>
-      <c r="BK7" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="BL7" s="6">
-        <v>5.2797999999999998E-2</v>
-      </c>
-      <c r="BM7" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN7" s="5">
-        <v>2.4660000000000001E-2</v>
-      </c>
-      <c r="BO7" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="BP7" s="6">
-        <v>1.6922E-2</v>
-      </c>
-      <c r="BQ7" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="BR7" s="5">
-        <v>-3.0980000000000001E-3</v>
-      </c>
-      <c r="BS7" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="BT7" s="6">
-        <v>-3.49E-3</v>
-      </c>
-      <c r="BU7" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="BV7" s="5">
-        <v>7.4715000000000004E-2</v>
-      </c>
-      <c r="BW7" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="BX7" s="6">
-        <v>0.26535599999999998</v>
-      </c>
-      <c r="BY7" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="BZ7" s="5">
-        <v>1.5993E-2</v>
-      </c>
-      <c r="CA7" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="CB7" s="6">
-        <v>0.24842800000000001</v>
-      </c>
-      <c r="CC7" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="CD7" s="5">
-        <v>-2.0805000000000001E-2</v>
-      </c>
-      <c r="CE7" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="CF7" s="6">
-        <v>-5.2692999999999997E-2</v>
-      </c>
-      <c r="CG7" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="CH7" s="5">
-        <v>-6.3105999999999995E-2</v>
-      </c>
-      <c r="CI7" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="CJ7" s="6">
-        <v>-8.8592000000000004E-2</v>
-      </c>
-      <c r="CK7" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="CP7" s="7" t="s">
+      <c r="AD7" s="10">
+        <v>6.1580490000000002E-2</v>
+      </c>
+      <c r="AE7" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="AF7" s="11">
+        <v>-0.23786667</v>
+      </c>
+      <c r="AG7" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH7" s="10">
+        <v>0.15430669</v>
+      </c>
+      <c r="AI7" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ7" s="11">
+        <v>1.8120939999999999E-2</v>
+      </c>
+      <c r="AK7" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="AL7" s="10"/>
+      <c r="AM7" s="10"/>
+      <c r="AN7" s="11"/>
+      <c r="AO7" s="11"/>
+      <c r="AP7" s="10"/>
+      <c r="AQ7" s="10"/>
+      <c r="AR7" s="11"/>
+      <c r="AS7" s="11"/>
+      <c r="AT7" s="10"/>
+      <c r="AU7" s="10"/>
+      <c r="AV7" s="11"/>
+      <c r="AW7" s="11"/>
+      <c r="AX7" s="10"/>
+      <c r="AY7" s="10"/>
+      <c r="AZ7" s="11"/>
+      <c r="BA7" s="11"/>
+      <c r="BB7" s="10"/>
+      <c r="BC7" s="10"/>
+      <c r="BD7" s="11"/>
+      <c r="BE7" s="11"/>
+      <c r="BF7" s="10"/>
+      <c r="BG7" s="10"/>
+      <c r="BH7" s="11"/>
+      <c r="BI7" s="11"/>
+      <c r="BJ7" s="10"/>
+      <c r="BK7" s="10"/>
+      <c r="BL7" s="11"/>
+      <c r="BM7" s="11"/>
+      <c r="BN7" s="10"/>
+      <c r="BO7" s="10"/>
+      <c r="BP7" s="11"/>
+      <c r="BQ7" s="11"/>
+      <c r="BR7" s="10"/>
+      <c r="BS7" s="10"/>
+      <c r="BT7" s="11"/>
+      <c r="BU7" s="11"/>
+      <c r="BV7" s="10"/>
+      <c r="BW7" s="10"/>
+      <c r="BX7" s="11"/>
+      <c r="BY7" s="11"/>
+      <c r="BZ7" s="10"/>
+      <c r="CA7" s="10"/>
+      <c r="CB7" s="11"/>
+      <c r="CC7" s="11"/>
+      <c r="CD7" s="10"/>
+      <c r="CE7" s="10"/>
+      <c r="CF7" s="11"/>
+      <c r="CG7" s="11"/>
+      <c r="CH7" s="12"/>
+      <c r="CI7" s="12"/>
+      <c r="CJ7" s="11"/>
+      <c r="CK7" s="11"/>
+      <c r="CL7" s="12"/>
+      <c r="CM7" s="12"/>
+      <c r="CN7" s="11"/>
+      <c r="CO7" s="11"/>
+      <c r="CP7" s="12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:94" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
+      <c r="A8" s="10">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0.74290666999999999</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-0.270903</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="B8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="10">
+        <v>-1.279741325</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0.197935</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="5">
-        <v>0.357983</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="F8" s="10">
+        <v>0.522922</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="6">
-        <v>0.16363800000000001</v>
-      </c>
-      <c r="I8" s="6" t="s">
+      <c r="H8" s="11">
+        <v>-0.31161100000000003</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0.102231</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="5">
-        <v>-2.0849859999999998</v>
-      </c>
-      <c r="K8" s="5" t="s">
+      <c r="L8" s="11">
+        <v>-0.30405599999999999</v>
+      </c>
+      <c r="M8" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="L8" s="6">
-        <v>-0.72388600000000003</v>
-      </c>
-      <c r="M8" s="6" t="s">
+      <c r="N8" s="10">
+        <v>-0.135656</v>
+      </c>
+      <c r="O8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="5">
-        <v>-0.50015799999999999</v>
-      </c>
-      <c r="O8" s="5" t="s">
+      <c r="P8" s="11">
+        <v>0.15152099999999999</v>
+      </c>
+      <c r="Q8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="P8" s="6">
-        <v>-0.442913</v>
-      </c>
-      <c r="Q8" s="6" t="s">
+      <c r="R8" s="10">
+        <v>-1.0688E-2</v>
+      </c>
+      <c r="S8" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="R8" s="5">
-        <v>-0.88647699999999996</v>
-      </c>
-      <c r="S8" s="5" t="s">
+      <c r="T8" s="11">
+        <v>1.5807999999999999E-2</v>
+      </c>
+      <c r="U8" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="V8" s="10">
+        <v>-2.9120000000000001E-3</v>
+      </c>
+      <c r="W8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="X8" s="11">
+        <v>6.6180000000000003E-2</v>
+      </c>
+      <c r="Y8" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="T8" s="6">
-        <v>0.11915100000000001</v>
-      </c>
-      <c r="U8" s="6" t="s">
+      <c r="Z8" s="10">
+        <v>2.1853000000000001E-2</v>
+      </c>
+      <c r="AA8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB8" s="11">
+        <v>-0.16267000000000001</v>
+      </c>
+      <c r="AC8" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD8" s="10">
+        <v>-3.2946000000000003E-2</v>
+      </c>
+      <c r="AE8" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF8" s="11">
+        <v>-0.22675500000000001</v>
+      </c>
+      <c r="AG8" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH8" s="10">
+        <v>2.3600000000000001E-3</v>
+      </c>
+      <c r="AI8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ8" s="11">
+        <v>8.8579999999999996E-3</v>
+      </c>
+      <c r="AK8" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL8" s="10">
+        <v>-1.5839999999999999E-3</v>
+      </c>
+      <c r="AM8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN8" s="11">
+        <v>-2.8802999999999999E-2</v>
+      </c>
+      <c r="AO8" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="V8" s="5">
-        <v>8.3213999999999996E-2</v>
-      </c>
-      <c r="W8" s="5" t="s">
+      <c r="AP8" s="10">
+        <v>-0.10467</v>
+      </c>
+      <c r="AQ8" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR8" s="11">
+        <v>-6.3159000000000007E-2</v>
+      </c>
+      <c r="AS8" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="X8" s="6">
-        <v>0.39572800000000002</v>
-      </c>
-      <c r="Y8" s="6" t="s">
+      <c r="AT8" s="10">
+        <v>0.101286</v>
+      </c>
+      <c r="AU8" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="Z8" s="5">
-        <v>-0.57014100000000001</v>
-      </c>
-      <c r="AA8" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="AB8" s="6">
-        <v>1.3962060000000001</v>
-      </c>
-      <c r="AC8" s="6" t="s">
+      <c r="AV8" s="11">
+        <v>-0.48324499999999998</v>
+      </c>
+      <c r="AW8" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="AX8" s="10">
+        <v>0.25268099999999999</v>
+      </c>
+      <c r="AY8" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="AD8" s="5">
-        <v>6.8970000000000004E-2</v>
-      </c>
-      <c r="AE8" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="AF8" s="6">
-        <v>-0.16877900000000001</v>
-      </c>
-      <c r="AG8" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="AH8" s="5">
-        <v>-0.68945000000000001</v>
-      </c>
-      <c r="AI8" s="5" t="s">
+      <c r="AZ8" s="11">
+        <v>-2.043E-2</v>
+      </c>
+      <c r="BA8" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="BB8" s="10">
+        <v>-7.6369999999999997E-3</v>
+      </c>
+      <c r="BC8" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="BD8" s="11">
+        <v>-5.1500000000000001E-3</v>
+      </c>
+      <c r="BE8" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="BF8" s="10">
+        <v>-1.7129999999999999E-3</v>
+      </c>
+      <c r="BG8" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="BH8" s="11">
+        <v>-5.9748999999999997E-2</v>
+      </c>
+      <c r="BI8" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="BJ8" s="10">
+        <v>-7.4051000000000006E-2</v>
+      </c>
+      <c r="BK8" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="BL8" s="11">
+        <v>5.2797999999999998E-2</v>
+      </c>
+      <c r="BM8" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="BN8" s="10">
+        <v>2.4660000000000001E-2</v>
+      </c>
+      <c r="BO8" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="BP8" s="11">
+        <v>1.6922E-2</v>
+      </c>
+      <c r="BQ8" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="BR8" s="10">
+        <v>-3.0980000000000001E-3</v>
+      </c>
+      <c r="BS8" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="BT8" s="11">
+        <v>-3.49E-3</v>
+      </c>
+      <c r="BU8" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="BV8" s="10">
+        <v>7.4715000000000004E-2</v>
+      </c>
+      <c r="BW8" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="BX8" s="11">
+        <v>0.26535599999999998</v>
+      </c>
+      <c r="BY8" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="BZ8" s="10">
+        <v>1.5993E-2</v>
+      </c>
+      <c r="CA8" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="CB8" s="11">
+        <v>0.24842800000000001</v>
+      </c>
+      <c r="CC8" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="CD8" s="10">
+        <v>-2.0805000000000001E-2</v>
+      </c>
+      <c r="CE8" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="CF8" s="11">
+        <v>-5.2692999999999997E-2</v>
+      </c>
+      <c r="CG8" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="AJ8" s="6">
-        <v>-0.74435499999999999</v>
-      </c>
-      <c r="AK8" s="6" t="s">
+      <c r="CH8" s="10">
+        <v>-6.3105999999999995E-2</v>
+      </c>
+      <c r="CI8" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="CJ8" s="11">
+        <v>-8.8592000000000004E-2</v>
+      </c>
+      <c r="CK8" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="CP8" s="7" t="s">
+      <c r="CL8" s="12"/>
+      <c r="CM8" s="12"/>
+      <c r="CN8" s="11"/>
+      <c r="CO8" s="11"/>
+      <c r="CP8" s="12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:94" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
+      <c r="A9" s="10">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-0.74286193</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0.270764</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="B9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.74290666999999999</v>
+      </c>
+      <c r="D9" s="11">
+        <v>-0.270903</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="5">
-        <v>-0.35805599999999999</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="F9" s="10">
+        <v>0.357983</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="6">
-        <v>-0.16356799999999999</v>
-      </c>
-      <c r="I9" s="6" t="s">
+      <c r="H9" s="11">
+        <v>0.16363800000000001</v>
+      </c>
+      <c r="I9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="5">
-        <v>2.0852400000000002</v>
-      </c>
-      <c r="K9" s="5" t="s">
+      <c r="J9" s="10">
+        <v>-2.0849859999999998</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="L9" s="6">
-        <v>0.72398899999999999</v>
-      </c>
-      <c r="M9" s="6" t="s">
+      <c r="L9" s="11">
+        <v>-0.72388600000000003</v>
+      </c>
+      <c r="M9" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="5">
-        <v>0.50011399999999995</v>
-      </c>
-      <c r="O9" s="5" t="s">
+      <c r="N9" s="10">
+        <v>-0.50015799999999999</v>
+      </c>
+      <c r="O9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P9" s="6">
-        <v>0.442747</v>
-      </c>
-      <c r="Q9" s="6" t="s">
+      <c r="P9" s="11">
+        <v>-0.442913</v>
+      </c>
+      <c r="Q9" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="R9" s="5">
-        <v>0.88661400000000001</v>
-      </c>
-      <c r="S9" s="5" t="s">
+      <c r="R9" s="10">
+        <v>-0.88647699999999996</v>
+      </c>
+      <c r="S9" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="T9" s="6">
-        <v>-0.11915199999999999</v>
-      </c>
-      <c r="U9" s="6" t="s">
+      <c r="T9" s="11">
+        <v>0.11915100000000001</v>
+      </c>
+      <c r="U9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="V9" s="5">
-        <v>-8.3404000000000006E-2</v>
-      </c>
-      <c r="W9" s="5" t="s">
+      <c r="V9" s="10">
+        <v>8.3213999999999996E-2</v>
+      </c>
+      <c r="W9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="X9" s="6">
-        <v>-0.39549299999999998</v>
-      </c>
-      <c r="Y9" s="6" t="s">
+      <c r="X9" s="11">
+        <v>0.39572800000000002</v>
+      </c>
+      <c r="Y9" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="Z9" s="5">
-        <v>0.57050599999999996</v>
-      </c>
-      <c r="AA9" s="5" t="s">
+      <c r="Z9" s="10">
+        <v>-0.57014100000000001</v>
+      </c>
+      <c r="AA9" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="AB9" s="6">
-        <v>-1.3965909999999999</v>
-      </c>
-      <c r="AC9" s="6" t="s">
+      <c r="AB9" s="11">
+        <v>1.3962060000000001</v>
+      </c>
+      <c r="AC9" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="AD9" s="5">
-        <v>-6.8986000000000006E-2</v>
-      </c>
-      <c r="AE9" s="5" t="s">
+      <c r="AD9" s="10">
+        <v>6.8970000000000004E-2</v>
+      </c>
+      <c r="AE9" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="AF9" s="6">
-        <v>0.16872599999999999</v>
-      </c>
-      <c r="AG9" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="AH9" s="5">
-        <v>0.689577</v>
-      </c>
-      <c r="AI9" s="5" t="s">
+      <c r="AF9" s="11">
+        <v>-0.16877900000000001</v>
+      </c>
+      <c r="AG9" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="AH9" s="10">
+        <v>-0.68945000000000001</v>
+      </c>
+      <c r="AI9" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="AJ9" s="6">
-        <v>0.74434400000000001</v>
-      </c>
-      <c r="AK9" s="6" t="s">
+      <c r="AJ9" s="11">
+        <v>-0.74435499999999999</v>
+      </c>
+      <c r="AK9" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="CP9" s="7" t="s">
+      <c r="AL9" s="10"/>
+      <c r="AM9" s="10"/>
+      <c r="AN9" s="11"/>
+      <c r="AO9" s="11"/>
+      <c r="AP9" s="10"/>
+      <c r="AQ9" s="10"/>
+      <c r="AR9" s="11"/>
+      <c r="AS9" s="11"/>
+      <c r="AT9" s="10"/>
+      <c r="AU9" s="10"/>
+      <c r="AV9" s="11"/>
+      <c r="AW9" s="11"/>
+      <c r="AX9" s="10"/>
+      <c r="AY9" s="10"/>
+      <c r="AZ9" s="11"/>
+      <c r="BA9" s="11"/>
+      <c r="BB9" s="10"/>
+      <c r="BC9" s="10"/>
+      <c r="BD9" s="11"/>
+      <c r="BE9" s="11"/>
+      <c r="BF9" s="10"/>
+      <c r="BG9" s="10"/>
+      <c r="BH9" s="11"/>
+      <c r="BI9" s="11"/>
+      <c r="BJ9" s="10"/>
+      <c r="BK9" s="10"/>
+      <c r="BL9" s="11"/>
+      <c r="BM9" s="11"/>
+      <c r="BN9" s="10"/>
+      <c r="BO9" s="10"/>
+      <c r="BP9" s="11"/>
+      <c r="BQ9" s="11"/>
+      <c r="BR9" s="10"/>
+      <c r="BS9" s="10"/>
+      <c r="BT9" s="11"/>
+      <c r="BU9" s="11"/>
+      <c r="BV9" s="10"/>
+      <c r="BW9" s="10"/>
+      <c r="BX9" s="11"/>
+      <c r="BY9" s="11"/>
+      <c r="BZ9" s="10"/>
+      <c r="CA9" s="10"/>
+      <c r="CB9" s="11"/>
+      <c r="CC9" s="11"/>
+      <c r="CD9" s="10"/>
+      <c r="CE9" s="10"/>
+      <c r="CF9" s="11"/>
+      <c r="CG9" s="11"/>
+      <c r="CH9" s="12"/>
+      <c r="CI9" s="12"/>
+      <c r="CJ9" s="11"/>
+      <c r="CK9" s="11"/>
+      <c r="CL9" s="12"/>
+      <c r="CM9" s="12"/>
+      <c r="CN9" s="11"/>
+      <c r="CO9" s="11"/>
+      <c r="CP9" s="12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:94" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
+      <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-0.22612088</v>
-      </c>
-      <c r="D10" s="9">
-        <v>-0.224966</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="B10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="10">
+        <v>-0.74286193</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0.270764</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="10">
-        <v>0.88305299999999998</v>
+        <v>-0.35805599999999999</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="9">
-        <v>-9.2086000000000001E-2</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>30</v>
+      <c r="H10" s="11">
+        <v>-0.16356799999999999</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="J10" s="10">
-        <v>-2.9132000000000002E-2</v>
+        <v>2.0852400000000002</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" s="9">
-        <v>-0.12656600000000001</v>
-      </c>
-      <c r="M10" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="11">
+        <v>0.72398899999999999</v>
+      </c>
+      <c r="M10" s="11" t="s">
         <v>32</v>
       </c>
       <c r="N10" s="10">
-        <v>7.7354000000000006E-2</v>
+        <v>0.50011399999999995</v>
       </c>
       <c r="O10" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P10" s="9">
-        <v>4.8980000000000003E-2</v>
-      </c>
-      <c r="Q10" s="9" t="s">
+      <c r="P10" s="11">
+        <v>0.442747</v>
+      </c>
+      <c r="Q10" s="11" t="s">
         <v>69</v>
       </c>
       <c r="R10" s="10">
-        <v>0.13153699999999999</v>
+        <v>0.88661400000000001</v>
       </c>
       <c r="S10" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="T10" s="9">
-        <v>-0.144624</v>
-      </c>
-      <c r="U10" s="9" t="s">
-        <v>48</v>
+      <c r="T10" s="11">
+        <v>-0.11915199999999999</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="V10" s="10">
-        <v>1.1126E-2</v>
+        <v>-8.3404000000000006E-2</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="X10" s="9">
-        <v>1.1738999999999999E-2</v>
-      </c>
-      <c r="Y10" s="9" t="s">
-        <v>76</v>
+        <v>49</v>
+      </c>
+      <c r="X10" s="11">
+        <v>-0.39549299999999998</v>
+      </c>
+      <c r="Y10" s="11" t="s">
+        <v>186</v>
       </c>
       <c r="Z10" s="10">
-        <v>2.8316999999999998E-2</v>
+        <v>0.57050599999999996</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB10" s="9">
-        <v>-0.59237399999999996</v>
-      </c>
-      <c r="AC10" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB10" s="11">
+        <v>-1.3965909999999999</v>
+      </c>
+      <c r="AC10" s="11" t="s">
         <v>184</v>
       </c>
       <c r="AD10" s="10">
-        <v>-1.8846999999999999E-2</v>
+        <v>-6.8986000000000006E-2</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF10" s="9">
-        <v>1.8606999999999999E-2</v>
-      </c>
-      <c r="AG10" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
+      </c>
+      <c r="AF10" s="11">
+        <v>0.16872599999999999</v>
+      </c>
+      <c r="AG10" s="11" t="s">
+        <v>176</v>
       </c>
       <c r="AH10" s="10">
-        <v>1.9474999999999999E-2</v>
+        <v>0.689577</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="AJ10" s="9">
-        <v>0.102933</v>
-      </c>
-      <c r="AK10" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL10" s="10">
-        <v>-6.1474000000000001E-2</v>
-      </c>
-      <c r="AM10" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="AN10" s="9">
-        <v>3.6558E-2</v>
-      </c>
-      <c r="AO10" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="AP10" s="10">
-        <v>0.16501299999999999</v>
-      </c>
-      <c r="AQ10" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="AR10" s="9">
-        <v>1.1609E-2</v>
-      </c>
-      <c r="AS10" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="AT10" s="10">
-        <v>2.6339999999999999E-2</v>
-      </c>
-      <c r="AU10" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="AV10" s="9">
-        <v>-2.4649999999999998E-2</v>
-      </c>
-      <c r="AW10" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="AX10" s="10">
-        <v>5.9039000000000001E-2</v>
-      </c>
-      <c r="AY10" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="AZ10" s="9">
-        <v>0.122209</v>
-      </c>
-      <c r="BA10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="BB10" s="10">
-        <v>9.8418000000000005E-2</v>
-      </c>
-      <c r="BC10" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="CP10" s="7" t="s">
+      <c r="AJ10" s="11">
+        <v>0.74434400000000001</v>
+      </c>
+      <c r="AK10" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL10" s="10"/>
+      <c r="AM10" s="10"/>
+      <c r="AN10" s="11"/>
+      <c r="AO10" s="11"/>
+      <c r="AP10" s="10"/>
+      <c r="AQ10" s="10"/>
+      <c r="AR10" s="11"/>
+      <c r="AS10" s="11"/>
+      <c r="AT10" s="10"/>
+      <c r="AU10" s="10"/>
+      <c r="AV10" s="11"/>
+      <c r="AW10" s="11"/>
+      <c r="AX10" s="10"/>
+      <c r="AY10" s="10"/>
+      <c r="AZ10" s="11"/>
+      <c r="BA10" s="11"/>
+      <c r="BB10" s="10"/>
+      <c r="BC10" s="10"/>
+      <c r="BD10" s="11"/>
+      <c r="BE10" s="11"/>
+      <c r="BF10" s="10"/>
+      <c r="BG10" s="10"/>
+      <c r="BH10" s="11"/>
+      <c r="BI10" s="11"/>
+      <c r="BJ10" s="10"/>
+      <c r="BK10" s="10"/>
+      <c r="BL10" s="11"/>
+      <c r="BM10" s="11"/>
+      <c r="BN10" s="10"/>
+      <c r="BO10" s="10"/>
+      <c r="BP10" s="11"/>
+      <c r="BQ10" s="11"/>
+      <c r="BR10" s="10"/>
+      <c r="BS10" s="10"/>
+      <c r="BT10" s="11"/>
+      <c r="BU10" s="11"/>
+      <c r="BV10" s="10"/>
+      <c r="BW10" s="10"/>
+      <c r="BX10" s="11"/>
+      <c r="BY10" s="11"/>
+      <c r="BZ10" s="10"/>
+      <c r="CA10" s="10"/>
+      <c r="CB10" s="11"/>
+      <c r="CC10" s="11"/>
+      <c r="CD10" s="10"/>
+      <c r="CE10" s="10"/>
+      <c r="CF10" s="11"/>
+      <c r="CG10" s="11"/>
+      <c r="CH10" s="12"/>
+      <c r="CI10" s="12"/>
+      <c r="CJ10" s="11"/>
+      <c r="CK10" s="11"/>
+      <c r="CL10" s="12"/>
+      <c r="CM10" s="12"/>
+      <c r="CN10" s="11"/>
+      <c r="CO10" s="11"/>
+      <c r="CP10" s="12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:94" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
+      <c r="A11" s="10">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-0.33903928999999999</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-0.162297</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="B11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="10">
+        <v>-0.22612088</v>
+      </c>
+      <c r="D11" s="11">
+        <v>-0.224966</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="5">
-        <v>-0.595974</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="F11" s="10">
+        <v>0.88305299999999998</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="6">
-        <v>-0.74608799999999997</v>
-      </c>
-      <c r="I11" s="6" t="s">
+      <c r="H11" s="11">
+        <v>-9.2086000000000001E-2</v>
+      </c>
+      <c r="I11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="5">
-        <v>-0.42910799999999999</v>
-      </c>
-      <c r="K11" s="5" t="s">
+      <c r="J11" s="10">
+        <v>-2.9132000000000002E-2</v>
+      </c>
+      <c r="K11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="L11" s="6">
-        <v>6.2303999999999998E-2</v>
-      </c>
-      <c r="M11" s="6" t="s">
+      <c r="L11" s="11">
+        <v>-0.12656600000000001</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="10">
+        <v>7.7354000000000006E-2</v>
+      </c>
+      <c r="O11" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="N11" s="5">
-        <v>-6.0245E-2</v>
-      </c>
-      <c r="O11" s="5" t="s">
+      <c r="P11" s="11">
+        <v>4.8980000000000003E-2</v>
+      </c>
+      <c r="Q11" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="P11" s="6">
-        <v>2.2263999999999999E-2</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="R11" s="5">
-        <v>-0.329654</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T11" s="6">
-        <v>-2.2048999999999999E-2</v>
-      </c>
-      <c r="U11" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="V11" s="5">
-        <v>-7.5092999999999993E-2</v>
-      </c>
-      <c r="W11" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="X11" s="6">
-        <v>-0.44991700000000001</v>
-      </c>
-      <c r="Y11" s="6" t="s">
+      <c r="R11" s="10">
+        <v>0.13153699999999999</v>
+      </c>
+      <c r="S11" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="T11" s="11">
+        <v>-0.144624</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="V11" s="10">
+        <v>1.1126E-2</v>
+      </c>
+      <c r="W11" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="X11" s="11">
+        <v>1.1738999999999999E-2</v>
+      </c>
+      <c r="Y11" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z11" s="10">
+        <v>2.8316999999999998E-2</v>
+      </c>
+      <c r="AA11" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB11" s="11">
+        <v>-0.59237399999999996</v>
+      </c>
+      <c r="AC11" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="AD11" s="10">
+        <v>-1.8846999999999999E-2</v>
+      </c>
+      <c r="AE11" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="AF11" s="11">
+        <v>1.8606999999999999E-2</v>
+      </c>
+      <c r="AG11" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="AH11" s="10">
+        <v>1.9474999999999999E-2</v>
+      </c>
+      <c r="AI11" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ11" s="11">
+        <v>0.102933</v>
+      </c>
+      <c r="AK11" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="AL11" s="10">
+        <v>-6.1474000000000001E-2</v>
+      </c>
+      <c r="AM11" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="Z11" s="5">
-        <v>0.58895799999999998</v>
-      </c>
-      <c r="AA11" s="5" t="s">
+      <c r="AN11" s="11">
+        <v>3.6558E-2</v>
+      </c>
+      <c r="AO11" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="AP11" s="10">
+        <v>0.16501299999999999</v>
+      </c>
+      <c r="AQ11" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="AR11" s="11">
+        <v>1.1609E-2</v>
+      </c>
+      <c r="AS11" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="AT11" s="10">
+        <v>2.6339999999999999E-2</v>
+      </c>
+      <c r="AU11" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="AV11" s="11">
+        <v>-2.4649999999999998E-2</v>
+      </c>
+      <c r="AW11" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="AX11" s="10">
+        <v>5.9039000000000001E-2</v>
+      </c>
+      <c r="AY11" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AB11" s="6">
-        <v>-0.19421099999999999</v>
-      </c>
-      <c r="AC11" s="6" t="s">
+      <c r="AZ11" s="11">
+        <v>0.122209</v>
+      </c>
+      <c r="BA11" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="AD11" s="5">
-        <v>-0.13211800000000001</v>
-      </c>
-      <c r="AE11" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="CP11" s="7" t="s">
+      <c r="BB11" s="10">
+        <v>9.8418000000000005E-2</v>
+      </c>
+      <c r="BC11" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="BD11" s="11"/>
+      <c r="BE11" s="11"/>
+      <c r="BF11" s="10"/>
+      <c r="BG11" s="10"/>
+      <c r="BH11" s="11"/>
+      <c r="BI11" s="11"/>
+      <c r="BJ11" s="10"/>
+      <c r="BK11" s="10"/>
+      <c r="BL11" s="11"/>
+      <c r="BM11" s="11"/>
+      <c r="BN11" s="10"/>
+      <c r="BO11" s="10"/>
+      <c r="BP11" s="11"/>
+      <c r="BQ11" s="11"/>
+      <c r="BR11" s="10"/>
+      <c r="BS11" s="10"/>
+      <c r="BT11" s="11"/>
+      <c r="BU11" s="11"/>
+      <c r="BV11" s="10"/>
+      <c r="BW11" s="10"/>
+      <c r="BX11" s="11"/>
+      <c r="BY11" s="11"/>
+      <c r="BZ11" s="10"/>
+      <c r="CA11" s="10"/>
+      <c r="CB11" s="11"/>
+      <c r="CC11" s="11"/>
+      <c r="CD11" s="10"/>
+      <c r="CE11" s="10"/>
+      <c r="CF11" s="11"/>
+      <c r="CG11" s="11"/>
+      <c r="CH11" s="12"/>
+      <c r="CI11" s="12"/>
+      <c r="CJ11" s="11"/>
+      <c r="CK11" s="11"/>
+      <c r="CL11" s="12"/>
+      <c r="CM11" s="12"/>
+      <c r="CN11" s="11"/>
+      <c r="CO11" s="11"/>
+      <c r="CP11" s="12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:94" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
+      <c r="A12" s="10">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="10">
+        <v>-0.33903928999999999</v>
+      </c>
+      <c r="D12" s="11">
+        <v>-0.162297</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="10">
+        <v>-0.595974</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="11">
+        <v>-0.74608799999999997</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="10">
+        <v>-0.42910799999999999</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="11">
+        <v>6.2303999999999998E-2</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="N12" s="10">
+        <v>-6.0245E-2</v>
+      </c>
+      <c r="O12" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P12" s="11">
+        <v>2.2263999999999999E-2</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="R12" s="10">
+        <v>-0.329654</v>
+      </c>
+      <c r="S12" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="T12" s="11">
+        <v>-2.2048999999999999E-2</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="V12" s="10">
+        <v>-7.5092999999999993E-2</v>
+      </c>
+      <c r="W12" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="X12" s="11">
+        <v>-0.44991700000000001</v>
+      </c>
+      <c r="Y12" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z12" s="10">
+        <v>0.58895799999999998</v>
+      </c>
+      <c r="AA12" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB12" s="11">
+        <v>-0.19421099999999999</v>
+      </c>
+      <c r="AC12" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD12" s="10">
+        <v>-0.13211800000000001</v>
+      </c>
+      <c r="AE12" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF12" s="11"/>
+      <c r="AG12" s="11"/>
+      <c r="AH12" s="10"/>
+      <c r="AI12" s="10"/>
+      <c r="AJ12" s="11"/>
+      <c r="AK12" s="11"/>
+      <c r="AL12" s="10"/>
+      <c r="AM12" s="10"/>
+      <c r="AN12" s="11"/>
+      <c r="AO12" s="11"/>
+      <c r="AP12" s="10"/>
+      <c r="AQ12" s="10"/>
+      <c r="AR12" s="11"/>
+      <c r="AS12" s="11"/>
+      <c r="AT12" s="10"/>
+      <c r="AU12" s="10"/>
+      <c r="AV12" s="11"/>
+      <c r="AW12" s="11"/>
+      <c r="AX12" s="10"/>
+      <c r="AY12" s="10"/>
+      <c r="AZ12" s="11"/>
+      <c r="BA12" s="11"/>
+      <c r="BB12" s="10"/>
+      <c r="BC12" s="10"/>
+      <c r="BD12" s="11"/>
+      <c r="BE12" s="11"/>
+      <c r="BF12" s="10"/>
+      <c r="BG12" s="10"/>
+      <c r="BH12" s="11"/>
+      <c r="BI12" s="11"/>
+      <c r="BJ12" s="10"/>
+      <c r="BK12" s="10"/>
+      <c r="BL12" s="11"/>
+      <c r="BM12" s="11"/>
+      <c r="BN12" s="10"/>
+      <c r="BO12" s="10"/>
+      <c r="BP12" s="11"/>
+      <c r="BQ12" s="11"/>
+      <c r="BR12" s="10"/>
+      <c r="BS12" s="10"/>
+      <c r="BT12" s="11"/>
+      <c r="BU12" s="11"/>
+      <c r="BV12" s="10"/>
+      <c r="BW12" s="10"/>
+      <c r="BX12" s="11"/>
+      <c r="BY12" s="11"/>
+      <c r="BZ12" s="10"/>
+      <c r="CA12" s="10"/>
+      <c r="CB12" s="11"/>
+      <c r="CC12" s="11"/>
+      <c r="CD12" s="10"/>
+      <c r="CE12" s="10"/>
+      <c r="CF12" s="11"/>
+      <c r="CG12" s="11"/>
+      <c r="CH12" s="12"/>
+      <c r="CI12" s="12"/>
+      <c r="CJ12" s="11"/>
+      <c r="CK12" s="11"/>
+      <c r="CL12" s="12"/>
+      <c r="CM12" s="12"/>
+      <c r="CN12" s="11"/>
+      <c r="CO12" s="11"/>
+      <c r="CP12" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:94" x14ac:dyDescent="0.2">
+      <c r="A13" s="10">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C13" s="10">
         <v>-1.6396963099999999</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D13" s="11">
         <v>0.98169200000000001</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F13" s="10">
         <v>1.7147870000000001</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H13" s="11">
         <v>1.0416019999999999</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I13" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J13" s="10">
         <v>-6.6109000000000001E-2</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K13" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L13" s="11">
         <v>-0.51912400000000003</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N13" s="10">
         <v>5.7883999999999998E-2</v>
       </c>
-      <c r="O12" s="5" t="s">
+      <c r="O13" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P13" s="11">
         <v>5.4393999999999998E-2</v>
       </c>
-      <c r="Q12" s="6" t="s">
+      <c r="Q13" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="R12" s="5">
+      <c r="R13" s="10">
         <v>-0.401001</v>
       </c>
-      <c r="S12" s="5" t="s">
+      <c r="S13" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="T12" s="6">
+      <c r="T13" s="11">
         <v>0.131768</v>
       </c>
-      <c r="U12" s="6" t="s">
+      <c r="U13" s="11" t="s">
         <v>167</v>
       </c>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="10"/>
+      <c r="AA13" s="10"/>
+      <c r="AB13" s="11"/>
+      <c r="AC13" s="11"/>
+      <c r="AD13" s="10"/>
+      <c r="AE13" s="10"/>
+      <c r="AF13" s="11"/>
+      <c r="AG13" s="11"/>
+      <c r="AH13" s="10"/>
+      <c r="AI13" s="10"/>
+      <c r="AJ13" s="11"/>
+      <c r="AK13" s="11"/>
+      <c r="AL13" s="10"/>
+      <c r="AM13" s="10"/>
+      <c r="AN13" s="11"/>
+      <c r="AO13" s="11"/>
+      <c r="AP13" s="10"/>
+      <c r="AQ13" s="10"/>
+      <c r="AR13" s="11"/>
+      <c r="AS13" s="11"/>
+      <c r="AT13" s="10"/>
+      <c r="AU13" s="10"/>
+      <c r="AV13" s="11"/>
+      <c r="AW13" s="11"/>
+      <c r="AX13" s="10"/>
+      <c r="AY13" s="10"/>
+      <c r="AZ13" s="11"/>
+      <c r="BA13" s="11"/>
+      <c r="BB13" s="10"/>
+      <c r="BC13" s="10"/>
+      <c r="BD13" s="11"/>
+      <c r="BE13" s="11"/>
+      <c r="BF13" s="10"/>
+      <c r="BG13" s="10"/>
+      <c r="BH13" s="11"/>
+      <c r="BI13" s="11"/>
+      <c r="BJ13" s="10"/>
+      <c r="BK13" s="10"/>
+      <c r="BL13" s="11"/>
+      <c r="BM13" s="11"/>
+      <c r="BN13" s="10"/>
+      <c r="BO13" s="10"/>
+      <c r="BP13" s="11"/>
+      <c r="BQ13" s="11"/>
+      <c r="BR13" s="10"/>
+      <c r="BS13" s="10"/>
+      <c r="BT13" s="11"/>
+      <c r="BU13" s="11"/>
+      <c r="BV13" s="10"/>
+      <c r="BW13" s="10"/>
+      <c r="BX13" s="11"/>
+      <c r="BY13" s="11"/>
+      <c r="BZ13" s="10"/>
+      <c r="CA13" s="10"/>
+      <c r="CB13" s="11"/>
+      <c r="CC13" s="11"/>
+      <c r="CD13" s="10"/>
+      <c r="CE13" s="10"/>
+      <c r="CF13" s="11"/>
+      <c r="CG13" s="11"/>
+      <c r="CH13" s="12"/>
+      <c r="CI13" s="12"/>
+      <c r="CJ13" s="11"/>
+      <c r="CK13" s="11"/>
+      <c r="CL13" s="12"/>
+      <c r="CM13" s="12"/>
+      <c r="CN13" s="11"/>
+      <c r="CO13" s="11"/>
+      <c r="CP13" s="12"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
